--- a/InputData/geoeng/ERWD/Enhanced Rock Weathering Data.xlsx
+++ b/InputData/geoeng/ERWD/Enhanced Rock Weathering Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rod\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\geoeng\ERWD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868C41B0-7E46-4805-952F-9E6033746016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8292E195-D03E-436C-A53F-858C90C19189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -611,28 +611,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="20.86328125" customWidth="1"/>
     <col min="2" max="2" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -640,102 +640,102 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B7" s="4">
         <v>2023</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
       <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B14" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A27" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A32">
         <v>0.88711067149387013</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -756,18 +756,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C706B8D-FB10-40CA-B025-270C2E82347D}">
   <dimension ref="A2:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" customWidth="1"/>
-    <col min="4" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
+    <col min="4" max="5" width="11.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="B2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -775,7 +775,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="44.25" x14ac:dyDescent="0.75">
       <c r="A4" s="6" t="s">
         <v>23</v>
       </c>
@@ -783,7 +783,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" s="6" t="s">
         <v>24</v>
       </c>
@@ -791,7 +791,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="44.25" x14ac:dyDescent="0.75">
       <c r="A6" s="6" t="s">
         <v>25</v>
       </c>
@@ -799,7 +799,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" s="6"/>
     </row>
   </sheetData>
@@ -815,15 +815,15 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AZ2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
-    <col min="2" max="21" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="32" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.86328125" customWidth="1"/>
+    <col min="2" max="21" width="9.40625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="32" width="9.40625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -981,7 +981,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1196,13 +1196,13 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AF11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AZ11"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -1299,8 +1299,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1313,7 +1373,7 @@
         <v>625559.22</v>
       </c>
       <c r="D2" s="5">
-        <f t="shared" ref="D2:AF2" si="0">$B$2</f>
+        <f t="shared" ref="D2:AZ2" si="0">$B$2</f>
         <v>625559.22</v>
       </c>
       <c r="E2" s="5">
@@ -1428,8 +1488,88 @@
         <f t="shared" si="0"/>
         <v>625559.22</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AH2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AI2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AJ2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AK2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AL2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AM2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AN2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AO2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AP2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AQ2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AR2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AS2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AT2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AU2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AV2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AW2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AX2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AY2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+      <c r="AZ2" s="5">
+        <f t="shared" si="0"/>
+        <v>625559.22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1526,8 +1666,68 @@
       <c r="AF3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1624,8 +1824,68 @@
       <c r="AF4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1722,8 +1982,68 @@
       <c r="AF5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1820,8 +2140,68 @@
       <c r="AF6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1918,8 +2298,68 @@
       <c r="AF7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -2016,8 +2456,68 @@
       <c r="AF8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -2114,8 +2614,68 @@
       <c r="AF9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -2212,8 +2772,68 @@
       <c r="AF10" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -2308,6 +2928,66 @@
         <v>0</v>
       </c>
       <c r="AF11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2321,13 +3001,13 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AZ2"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="1" max="1" width="24.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>39</v>
       </c>
@@ -2424,8 +3104,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -2551,6 +3291,86 @@
       </c>
       <c r="AF2">
         <f>'Fuhrman data'!B3*About!A32</f>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AG2">
+        <f>AF2</f>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ2" si="1">AG2</f>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="1"/>
+        <v>79.839960434448315</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="1"/>
         <v>79.839960434448315</v>
       </c>
     </row>
@@ -2560,6 +3380,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2675f8417a7852adb5ac278d647999f1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d431266b3277f48244cbeea34d4f4da" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -2703,23 +3538,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E93C57EC-BE0D-430E-B991-451E702B3440}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEC54658-8104-4245-A3F1-446D31C07976}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2739,9 +3563,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEC54658-8104-4245-A3F1-446D31C07976}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E93C57EC-BE0D-430E-B991-451E702B3440}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>